--- a/rcads/data/xls/32_CodebookOptionMap.xlsx
+++ b/rcads/data/xls/32_CodebookOptionMap.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_32_CodebookOptionMap"/>
   </sheets>
   <definedNames>
-    <definedName name="_32_CodebookOptionMap">'_32_CodebookOptionMap'!$A$1:$E$153</definedName>
+    <definedName name="_32_CodebookOptionMap">'_32_CodebookOptionMap'!$A$1:$E$157</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -2957,6 +2957,74 @@
         <v>3</v>
       </c>
     </row>
+    <row outlineLevel="0" r="154">
+      <c r="A154" s="0">
+        <v>153</v>
+      </c>
+      <c r="B154" s="0">
+        <v>39</v>
+      </c>
+      <c r="C154" s="0">
+        <v>152</v>
+      </c>
+      <c r="D154" s="0">
+        <v>1</v>
+      </c>
+      <c r="E154" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="155">
+      <c r="A155" s="0">
+        <v>154</v>
+      </c>
+      <c r="B155" s="0">
+        <v>39</v>
+      </c>
+      <c r="C155" s="0">
+        <v>153</v>
+      </c>
+      <c r="D155" s="0">
+        <v>2</v>
+      </c>
+      <c r="E155" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="156">
+      <c r="A156" s="0">
+        <v>155</v>
+      </c>
+      <c r="B156" s="0">
+        <v>39</v>
+      </c>
+      <c r="C156" s="0">
+        <v>154</v>
+      </c>
+      <c r="D156" s="0">
+        <v>3</v>
+      </c>
+      <c r="E156" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="157">
+      <c r="A157" s="0">
+        <v>156</v>
+      </c>
+      <c r="B157" s="0">
+        <v>39</v>
+      </c>
+      <c r="C157" s="0">
+        <v>76</v>
+      </c>
+      <c r="D157" s="0">
+        <v>4</v>
+      </c>
+      <c r="E157" s="0">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/rcads/data/xls/32_CodebookOptionMap.xlsx
+++ b/rcads/data/xls/32_CodebookOptionMap.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_32_CodebookOptionMap"/>
   </sheets>
   <definedNames>
-    <definedName name="_32_CodebookOptionMap">'_32_CodebookOptionMap'!$A$1:$E$157</definedName>
+    <definedName name="_32_CodebookOptionMap">'_32_CodebookOptionMap'!$A$1:$E$173</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E157"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -3025,6 +3025,278 @@
         <v>3</v>
       </c>
     </row>
+    <row outlineLevel="0" r="158">
+      <c r="A158" s="0">
+        <v>157</v>
+      </c>
+      <c r="B158" s="0">
+        <v>40</v>
+      </c>
+      <c r="C158" s="0">
+        <v>156</v>
+      </c>
+      <c r="D158" s="0">
+        <v>1</v>
+      </c>
+      <c r="E158" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="159">
+      <c r="A159" s="0">
+        <v>158</v>
+      </c>
+      <c r="B159" s="0">
+        <v>40</v>
+      </c>
+      <c r="C159" s="0">
+        <v>157</v>
+      </c>
+      <c r="D159" s="0">
+        <v>2</v>
+      </c>
+      <c r="E159" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="160">
+      <c r="A160" s="0">
+        <v>159</v>
+      </c>
+      <c r="B160" s="0">
+        <v>40</v>
+      </c>
+      <c r="C160" s="0">
+        <v>158</v>
+      </c>
+      <c r="D160" s="0">
+        <v>3</v>
+      </c>
+      <c r="E160" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="161">
+      <c r="A161" s="0">
+        <v>160</v>
+      </c>
+      <c r="B161" s="0">
+        <v>40</v>
+      </c>
+      <c r="C161" s="0">
+        <v>159</v>
+      </c>
+      <c r="D161" s="0">
+        <v>4</v>
+      </c>
+      <c r="E161" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="162">
+      <c r="A162" s="0">
+        <v>161</v>
+      </c>
+      <c r="B162" s="0">
+        <v>41</v>
+      </c>
+      <c r="C162" s="0">
+        <v>160</v>
+      </c>
+      <c r="D162" s="0">
+        <v>1</v>
+      </c>
+      <c r="E162" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="163">
+      <c r="A163" s="0">
+        <v>162</v>
+      </c>
+      <c r="B163" s="0">
+        <v>41</v>
+      </c>
+      <c r="C163" s="0">
+        <v>161</v>
+      </c>
+      <c r="D163" s="0">
+        <v>2</v>
+      </c>
+      <c r="E163" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="164">
+      <c r="A164" s="0">
+        <v>163</v>
+      </c>
+      <c r="B164" s="0">
+        <v>41</v>
+      </c>
+      <c r="C164" s="0">
+        <v>162</v>
+      </c>
+      <c r="D164" s="0">
+        <v>3</v>
+      </c>
+      <c r="E164" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="165">
+      <c r="A165" s="0">
+        <v>164</v>
+      </c>
+      <c r="B165" s="0">
+        <v>41</v>
+      </c>
+      <c r="C165" s="0">
+        <v>163</v>
+      </c>
+      <c r="D165" s="0">
+        <v>4</v>
+      </c>
+      <c r="E165" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="166">
+      <c r="A166" s="0">
+        <v>165</v>
+      </c>
+      <c r="B166" s="0">
+        <v>42</v>
+      </c>
+      <c r="C166" s="0">
+        <v>160</v>
+      </c>
+      <c r="D166" s="0">
+        <v>1</v>
+      </c>
+      <c r="E166" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="167">
+      <c r="A167" s="0">
+        <v>166</v>
+      </c>
+      <c r="B167" s="0">
+        <v>42</v>
+      </c>
+      <c r="C167" s="0">
+        <v>161</v>
+      </c>
+      <c r="D167" s="0">
+        <v>2</v>
+      </c>
+      <c r="E167" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="168">
+      <c r="A168" s="0">
+        <v>167</v>
+      </c>
+      <c r="B168" s="0">
+        <v>42</v>
+      </c>
+      <c r="C168" s="0">
+        <v>164</v>
+      </c>
+      <c r="D168" s="0">
+        <v>3</v>
+      </c>
+      <c r="E168" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="169">
+      <c r="A169" s="0">
+        <v>168</v>
+      </c>
+      <c r="B169" s="0">
+        <v>42</v>
+      </c>
+      <c r="C169" s="0">
+        <v>163</v>
+      </c>
+      <c r="D169" s="0">
+        <v>4</v>
+      </c>
+      <c r="E169" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="170">
+      <c r="A170" s="0">
+        <v>169</v>
+      </c>
+      <c r="B170" s="0">
+        <v>43</v>
+      </c>
+      <c r="C170" s="0">
+        <v>165</v>
+      </c>
+      <c r="D170" s="0">
+        <v>1</v>
+      </c>
+      <c r="E170" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="171">
+      <c r="A171" s="0">
+        <v>170</v>
+      </c>
+      <c r="B171" s="0">
+        <v>43</v>
+      </c>
+      <c r="C171" s="0">
+        <v>166</v>
+      </c>
+      <c r="D171" s="0">
+        <v>2</v>
+      </c>
+      <c r="E171" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="172">
+      <c r="A172" s="0">
+        <v>171</v>
+      </c>
+      <c r="B172" s="0">
+        <v>43</v>
+      </c>
+      <c r="C172" s="0">
+        <v>167</v>
+      </c>
+      <c r="D172" s="0">
+        <v>3</v>
+      </c>
+      <c r="E172" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="173">
+      <c r="A173" s="0">
+        <v>172</v>
+      </c>
+      <c r="B173" s="0">
+        <v>43</v>
+      </c>
+      <c r="C173" s="0">
+        <v>168</v>
+      </c>
+      <c r="D173" s="0">
+        <v>4</v>
+      </c>
+      <c r="E173" s="0">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
